--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_08_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_08_18_Cau.xlsx
@@ -639,7 +639,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt đối tượng truyền tải với từng phần dữ liệu nội dung.</t>
+          <t>Khi một hàm trả về stream (iterator các chunk/event) trong khi bên gọi cần chuỗi hoàn chỉnh, lỗi là iterator chưa được duyệt và các delta nội dung chưa được trích xuất để ghép nối lại thành một chuỗi text hoàn chỉnh.</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng số thứ tự, không dùng thứ tự các phần tử đến.</t>
+          <t>Khi các delta đến lệch thứ tự (3,'C'), (1,'A'), (2,'B'), hợp đồng yêu cầu phát theo số thứ tự: Thứ tự 1: A (o2) -&gt; Thứ tự 2: B (o3) -&gt; Thứ tự 3: C (o1).</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi kết quả từng phần có an toàn và hữu ích trước khi hoàn tất hay không.</t>
+          <t>Cuộc trò chuyện dài, người dùng chấp nhận đọc dần (x1) dùng truyền kết quả từng phần streaming (r1); JSON phải kiểm tra toàn bộ trước khi hệ thống tài chính nhận (x2) cần giữ toàn bộ kết quả rồi kiểm tra trước khi chuyển tiếp (r2); Xử lý theo lô ở chế độ ngoại tuyến không người chờ (x3) dùng thu thập theo lô đơn giản (r3).</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ràng buộc quyết định là `trước khi hiển thị bất kỳ byte nào`.</t>
+          <t>Nếu ứng dụng có yêu cầu bắt buộc phải kiểm tra schema và chữ ký trên toàn bộ phản hồi trước khi hiển thị bất kỳ byte nào, chế độ phù hợp trực tiếp là không streaming hoặc phải đệm (buffer) toàn bộ response rồi mới hiển thị.</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi câu trả lời của assistant phải đứng sau lượt user mà nó trả lời.</t>
+          <t>Thứ tự hội thoại theo thời gian bắt đầu từ trạng thái rỗng là: user:U1 (o2) -&gt; assistant:A1 (o3) -&gt; user:U2 (o4) -&gt; assistant:A2 (o1).</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một policy tốt phải có quy tắc có thể kiểm thử và giữ trình tự cùng state cần thiết.</t>
+          <t>Các chính sách quản lý state hội thoại có kiểm soát gồm: Giữ N lượt gần nhất (sliding window) (a), Tóm tắt lượt cũ và giữ lượt gần đây (b), và Truy xuất state/fact liên quan theo ngữ cảnh (c). Xáo trộn hoặc xóa ngẫu nhiên làm hỏng tính mạch lạc.</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ retry lỗi có khả năng tự thay đổi theo thời gian mà không cần sửa request hoặc credential.</t>
+          <t>Lỗi có thể retry là lỗi tạm thời có khả năng tự phục hồi: Timeout mạng tạm thời (a), Lỗi rate-limit 429 có Retry-After (b), và Lỗi 503 Service Unavailable tạm thời (e). Lỗi sai API key (c) và malformed schema (d) là lỗi 4xx cố định, không được retry.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi người kiểm thử cần biết gì để quyết định phần triển khai đạt hay không.</t>
+          <t>Đặc tả kiểm thử được cần: Định dạng/kích thước file và xử lý lỗi (a), Luồng giao diện/API (b), Ràng buộc bảo mật và lưu trữ (c), cùng Tiêu chí chấp nhận kiểm thử được (d).</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một bài kiểm thử phải có thể trả kết quả đạt/không đạt từ hành vi cụ thể.</t>
+          <t>Tiêu chí chấp nhận kiểm thử được phải có đầu vào cụ thể, hành vi quan sát được và kết quả đạt/không đạt rõ ràng: 'Với CSV amount gồm 2, 3 và một dòng trống, hàm trả 5 và không gọi mạng'.</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn hành động tạo bằng chứng quan sát được về hành vi so với contract.</t>
+          <t>Bằng chứng kiểm chứng trực tiếp gồm: Đối chiếu tiêu chí chấp nhận với code/test (a), Chạy bộ test đường bình thường và test biên/đối nghịch (b), và Kiểm tra hậu quả lỗi cùng regression test (d). Tin tưởng vì mã trông trôi chảy (c) hay hỏi lại mô hình (e) không tạo bằng chứng kiểm thử khách quan.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_08_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_01_Full_150_Cau/Day_01_Ngan_Hang_Phan_08_18_Cau.xlsx
@@ -810,10 +810,17 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So hai chỉ số: lúc người dùng thấy phần đầu và lúc phản hồi hoàn tất.
-Phân tích theo nguyên lý thiết kế: So hai chỉ số: lúc người dùng thấy phần đầu và lúc phản hồi hoàn tất.</t>
+- Giải thích lý do chọn streaming (1.5 điểm): Phân tích tối ưu Perceived Latency và chỉ số Time to First Token (TTFT = 0,5s) giúp người dùng đọc ngay lập tức.
+- Khẳng định điều không đúng (1.5 điểm): Nêu rõ streaming không làm giảm tổng thời gian hoàn thành (vẫn 2 phút) và không tăng throughput phần cứng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Vì sao vẫn chọn chế độ streaming:
+Mặc dù tổng thời gian hoàn tất tác vụ không đổi (vẫn mất 2 phút), streaming tối ưu hóa triệt để cảm nhận thời gian chờ đợi của người dùng (Perceived Latency). Chỉ số Thời gian đến token đầu tiên (Time to First Token - TTFT) giảm ngoạn mục xuống chỉ còn 0,5 giây. Người dùng có thể bắt đầu đọc, tiếp thu và thực hiện ngay các bước hướng dẫn ban đầu trong khi mô hình tiếp tục sinh các bước tiếp theo, loại bỏ hoàn toàn cảm giác hệ thống bị đơ hay phản hồi chậm.
+2. Điều gì KHÔNG ĐƯỢC khẳng định:
+KHÔNG ĐƯỢC khẳng định rằng streaming làm giảm tổng thời gian xử lý của hệ thống (Total Request Latency / Generation Time) hoặc làm tăng thông lượng (throughput) của máy chủ. Tổng thời gian chạy và lượng tính toán tiêu thụ trên GPU giữa hai chế độ là hoàn toàn như nhau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên tắc thiết kế trải nghiệm người dùng trong AI (HCI / UX for AI) phân biệt rõ giữa Tốc độ thực tế (Actual Performance) và Tốc độ cảm nhận (Perceived Performance). Với các tác vụ sinh nội dung dài (long-form generation), TTFT dưới 1 giây giữ người dùng ở lại trong trạng thái tập trung liên tục (flow state).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nielsen Norman Group - Response Times: The 3 Important Limits (https://www.nngroup.com/articles/response-times-3-important-limits/); Vercel AI SDK - UX Principles.</t>
         </is>
       </c>
     </row>
@@ -892,10 +899,18 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đếm theo cặp user+assistant, không theo số message rời.
-Phân tích theo nguyên lý thiết kế: Đếm theo cặp user+assistant, không theo số message rời.</t>
+- Xác định đúng lịch sử cần gửi (2.0 điểm): Nêu chính xác danh sách gồm 2 cặp `[U2, A2, U3, A3]`.
+- Giải thích loại bỏ cặp cũ nhất (1.0 điểm): Giải thích rõ cặp `[U1, A1]` bị cắt tỉa do vượt quá ngưỡng giới hạn 2 cặp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Theo chính sách lưu giữ tối đa 2 cặp user/assistant hoàn chỉnh gần nhất, lịch sử hội thoại được gửi trước `U4` là:
+```
+[U2, A2, U3, A3]
+```
+Giải thích: Lịch sử hiện tại gồm 3 cặp hoàn chỉnh: Cặp 1 (`U1, A1`), Cặp 2 (`U2, A2`), Cặp 3 (`U3, A3`). Chính sách cửa sổ trượt (Sliding Window Policy) yêu cầu chỉ giữ lại 2 cặp gần nhất, do đó cặp cũ nhất `[U1, A1]` bị loại bỏ. Request tiếp theo khi người dùng gửi `U4` sẽ chứa lịch sử gồm `[U2, A2, U3, A3]` theo sau bởi câu hỏi mới `U4`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Quản lý bộ nhớ hội thoại theo cặp hoàn chỉnh (Conversation Pair-based Windowing) đảm bảo mô hình luôn nhận được ngữ cảnh cân bằng giữa câu hỏi và câu trả lời tương ứng. Tránh tình trạng cắt lẻ tẻ từng message làm mất tính toàn vẹn của lượt hội thoại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation - Memory: ConversationBufferWindowMemory (https://python.langchain.com/docs/modules/memory/); Semantic Kernel Context Management.</t>
         </is>
       </c>
     </row>
@@ -982,10 +997,19 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chỉ chờ sau thất bại nếu vẫn còn lần thử tiếp theo.
-Phân tích theo nguyên lý thiết kế: Chỉ chờ sau thất bại nếu vẫn còn lần thử tiếp theo.</t>
+- Tính chính xác các khoảng chờ (2.0 điểm): Tính đúng 3 khoảng chờ lần lượt là 1 giây, 2 giây và 4 giây.
+- Giải thích không chờ sau lần 4 (1.0 điểm): Nêu rõ lần thử 4 thành công nên kết thúc quy trình, không phát sinh thời gian chờ tiếp theo.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tính toán các khoảng thời gian chờ thực tế giữa các lần thử theo công thức $Delay = 1 \times 2^{(\text{attempt\_index} - 1)}$ giây:
+1. Lần thử 1 thất bại (attempt_index = 1): Khoảng chờ trước lần thử 2 là $1 \times 2^{1 - 1} = 1 \times 2^0 = 1$ giây.
+2. Lần thử 2 thất bại (attempt_index = 2): Khoảng chờ trước lần thử 3 là $1 \times 2^{2 - 1} = 1 \times 2^1 = 2$ giây.
+3. Lần thử 3 thất bại (attempt_index = 3): Khoảng chờ trước lần thử 4 là $1 \times 2^{3 - 1} = 1 \times 2^2 = 4$ giây.
+4. Lần thử 4 thành công: Không có khoảng chờ sau lần thử 4 vì tác vụ đã hoàn tất thành công.
+Kết luận: Các khoảng chờ thực tế lần lượt là: 1 giây, 2 giây, và 4 giây (tổng thời gian chờ giữa các lần thử là $1 + 2 + 4 = 7$ giây).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Thuật toán Exponential Backoff kéo giãn thời gian chờ theo hàm mũ sau mỗi lần lỗi, giúp hệ thống hạ lưu (downstream service) có thời gian hồi phục sau sự cố quá tải tạm thời (transient overload), ngăn chặn hiện tượng giông bão yêu cầu (Thundering Herd Problem).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+AWS Architecture Blog - Exponential Backoff And Jitter (https://aws.amazon.com/blogs/architecture/exponential-backoff-and-jitter/); Google Cloud Retry Guidance.</t>
         </is>
       </c>
     </row>
@@ -1060,10 +1084,17 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 3 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi khoảng chờ phải chuẩn bị cho một lần thử tiếp theo.
-Phân tích theo nguyên lý thiết kế: Mỗi khoảng chờ phải chuẩn bị cho một lần thử tiếp theo.</t>
+- Hành động sau lần thử cuối (1.5 điểm): Nêu rõ việc dừng retry, ghi log lỗi E3 và ném ngoại lệ thất bại (fail-fast).
+- Giải thích lý do không chờ thêm (1.5 điểm): Phân tích việc hết ngân sách thử (đã đủ 3 lần) khiến việc chờ thêm không phục vụ mục đích nào, gây treo tài nguyên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Hành động phải làm sau lần thử thứ 3 thất bại:
+Hệ thống phải lập tức dừng quy trình retry, ghi log chi tiết lỗi cuối cùng E3 (kèm thông tin context và stack trace), và ném ra ngoại lệ thất bại (raise Exception) hoặc trả về mã lỗi thất bại dứt điểm (ví dụ HTTP 503 / 500) cho phía gọi (Fail-Fast).
+2. Vì sao không chờ thêm:
+Bởi vì chính sách chỉ cho phép tối đa 3 lần thử (max attempts = 3). Mọi khoảng chờ trong cơ chế retry chỉ có ý nghĩa khi có một lần thử tiếp theo được lên lịch để bù đắp. Khi đã chạm ngưỡng thử tối đa mà không còn lần thử nào nữa, việc chờ thêm là hoàn toàn vô ích, gây lãng phí tài nguyên luồng thực thi (blocked worker threads) và làm tăng độ trễ vô nghĩa cho client.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Nguyên lý Fail-Fast và Resource Conservation trong thiết kế hệ thống phân tán quy định: Khi một tác vụ đã sử dụng hết ngân sách thử lại (retry budget), hệ thống phải giải phóng tài nguyên ngay lập tức để bảo vệ tính sẵn sàng của toàn hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Addressing Cascading Failures &amp; Retry Budgets (https://sre.google/sre-book/addressing-cascading-failures/); Microsoft Cloud Design Patterns - Retry Pattern.</t>
         </is>
       </c>
     </row>
@@ -1202,10 +1233,28 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi tiêu chí chấp nhận nên có đầu vào/điều kiện và kết quả quan sát được mong đợi.
-Phân tích theo nguyên lý thiết kế: Mỗi tiêu chí chấp nhận nên có đầu vào/điều kiện và kết quả quan sát được mong đợi.</t>
+- Giao diện hàm rõ ràng (1.0 điểm): Định nghĩa đúng signature có kiểu dữ liệu đầu vào `csv_file_path: str` và đầu ra `float`.
+- Tiêu chí tính tổng &amp; bỏ dòng trống (1.0 điểm): Nêu rõ test case tính đúng số tiền và bỏ qua các dòng trống an toàn.
+- Tiêu chí báo lỗi thiếu cột (1.0 điểm): Quy định ném ngoại lệ `ValueError` khi file thiếu cột `'amount'`.
+- Ràng buộc không dùng mạng (1.0 điểm): Khẳng định thực thi hoàn toàn cục bộ, không mở kết nối socket mạng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bản mô tả yêu cầu kỹ thuật và tiêu chí chấp nhận cho hàm Python:
+### 1. GIAO DIỆN HÀM (FUNCTION SIGNATURE)
+```python
+def calculate_total_amount(csv_file_path: str) -&gt; float:
+    """
+    Đọc file CSV cục bộ, tính tổng các giá trị trong cột 'amount' và trả về số thực.
+    """
+```
+### 2. CÁC TIÊU CHÍ CHẤP NHẬN (ACCEPTANCE CRITERIA)
+- Tiêu chí 1 (Happy Path - Tính tổng chuẩn xác): Khi truyền đường dẫn đến một file CSV hợp lệ có cột `amount` (ví dụ chứa các giá trị 10.5, 20.0, 5.5), hàm trả về kết quả số thực chính xác là `36.0`.
+- Tiêu chí 2 (Bỏ qua dòng trống): Các dòng hoàn toàn trống, dòng chỉ chứa khoảng trắng hoặc dấu phẩy rỗng giữa các dòng dữ liệu không được gây lỗi và phải được tự động bỏ qua khi tính toán.
+- Tiêu chí 3 (Báo lỗi khi thiếu cột bắt buộc): Nếu file CSV tồn tại nhưng không chứa cột có tiêu đề chính xác là `'amount'`, hàm phải ném ra ngoại lệ `ValueError` với thông báo rõ ràng: `"Missing required 'amount' column"`.
+- Tiêu chí 4 (Cô lập ngoại vi &amp; Không kết nối mạng): Toàn bộ thao tác chỉ sử dụng thư viện chuẩn của Python (`csv` hoặc `pathlib`), thực thi 100% trên hệ thống file cục bộ, không mở bất kỳ kết nối socket/HTTP mạng nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Bản đặc tả kỹ thuật tiêu chuẩn (Executable Specification / Given-When-Then) cần định nghĩa ranh giới rõ ràng về kiểu dữ liệu (Type hinting), các kịch bản thành công, xử lý biên (empty rows), điều kiện lỗi (error handling) và các ràng buộc phi chức năng (no network).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler - Specification by Example (https://martinfowler.com/bliki/GivenWhenThen.html); Python Documentation - csv module.</t>
         </is>
       </c>
     </row>
@@ -1291,10 +1340,32 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So hành vi mong đợi khi b=0 với đường đi thực tế của lệnh `return`.
-Phân tích theo nguyên lý thiết kế: So hành vi mong đợi khi b=0 với đường đi thực tế của lệnh `return`.</t>
+- Chỉ ra lỗi sai hợp đồng (1.5 điểm): Nêu rõ hàm trả về 0 thay vì ném ngoại lệ `ValueError` khi `b == 0`.
+- Viết bài kiểm thử pytest chuẩn (1.5 điểm): Viết test case sử dụng `pytest.raises(ValueError)` để kiểm tra ngoại lệ.
+- Sửa mã nguồn chính xác (1.0 điểm): Cập nhật code với lệnh `raise ValueError(...)` khi `b == 0`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra lỗi trong mã do AI sinh:
+Khi `b == 0`, hàm trả về giá trị `0` (`return 0`) thay vì ném ra ngoại lệ `ValueError` theo đúng yêu cầu đặc tả. Điều này làm sai lệch ngữ nghĩa toán học (phép chia cho 0 là không xác định) và che giấu lỗi nghiêm trọng, khiến các phép tính phía sau tiếp tục chạy với dữ liệu sai.
+2. Viết bài kiểm thử tối thiểu (sử dụng pytest):
+```python
+import pytest
+def test_safe_divide_by_zero_raises_value_error():
+    with pytest.raises(ValueError, match="Cannot divide by zero"):
+        safe_divide(10, 0)
+def test_safe_divide_valid():
+    assert safe_divide(10, 2) == 5.0
+```
+3. Sửa mã nguồn chuẩn xác:
+```python
+def safe_divide(a, b):
+    if b == 0:
+        raise ValueError("Cannot divide by zero")
+    return a / b
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Đây là lỗi vi phạm hợp đồng hàm (Contract Violation) rất phổ biến trong code do AI sinh: AI có xu hướng 'nuốt lỗi' bằng cách trả về giá trị mặc định (như 0 hoặc None) thay vì raise exception. Điều này vi phạm nguyên tắc Fail-Fast của kỹ nghệ phần mềm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Python Software Foundation - Built-in Exceptions (https://docs.python.org/3/library/exceptions.html); Pytest Documentation - Asserting Expected Exceptions.</t>
         </is>
       </c>
     </row>
@@ -1330,10 +1401,37 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nối chuỗi base không bảo đảm đường dẫn sau khi chuẩn hóa vẫn nằm bên dưới thư mục gốc.
-Phân tích theo nguyên lý thiết kế: Nối chuỗi base không bảo đảm đường dẫn sau khi chuẩn hóa vẫn nằm bên dưới thư mục gốc.</t>
+- Nhận diện đúng rủi ro Path Traversal (1.5 điểm): Gọi tên chính xác lỗ hổng Path Traversal (CWE-22) và giải thích cơ chế thoát khỏi `/tmp/reports` qua `../../`.
+- Viết test case bảo mật (1.5 điểm): Viết test kiểm tra ném ngoại lệ khi gặp input nguy hại `../../secret`.
+- Đề xuất code sửa an toàn (1.0 điểm): Sử dụng `Path.resolve()` và kiểm tra đường dẫn đích phải nằm trong `base_dir`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Rủi ro bảo mật:
+Lỗ hổng Path Traversal (Directory Traversal - CWE-22). Phép nối chuỗi thô `'/tmp/reports/' + name` cho phép kẻ tấn công truyền vào chuỗi `'../../secret'`. Khi chuẩn hóa đường dẫn, `'/tmp/reports/../../secret'` sẽ phân giải thành `'/secret'`, cho phép ghi đè hoặc tạo file tùy ý ra ngoài thư mục an toàn `/tmp/reports`, gây nguy cơ ghi đè cấu hình hệ thống hoặc chiếm quyền điều khiển máy chủ.
+2. Viết một bài kiểm thử bảo mật (pytest):
+```python
+import pytest
+from pathlib import Path
+def test_path_traversal_prevention(tmp_path):
+    malicious_input = "../../secret"
+    with pytest.raises(ValueError, match="Access denied: Path traversal detected"):
+        safe_open_report(malicious_input)
+```
+3. Đề xuất hướng sửa mã nguồn an toàn:
+Sử dụng thư viện `pathlib.Path` để phân giải đường dẫn tuyệt đối (canonical path) và kiểm tra xem đường dẫn đích có nằm bên trong thư mục gốc hay không:
+```python
+from pathlib import Path
+def safe_open_report(name: str):
+    base_dir = Path("/tmp/reports").resolve()
+    target_path = (base_dir / name).resolve()
+    # Kiểm tra đường dẫn đích có bắt đầu bằng thư mục an toàn
+    if not str(target_path).startswith(str(base_dir) + "/") and target_path != base_dir:
+        raise ValueError("Access denied: Path traversal detected")
+    return open(target_path, "w")
+```
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phân tích theo nguyên lý thiết kế: Lỗ hổng CWE-22 xảy ra khi mã nguồn tin tưởng mù quáng vào input của người dùng để ghép đường dẫn file. Biện pháp phòng ngừa chuẩn tắc là luôn chuẩn hóa đường dẫn (Canonicalization) bằng `resolve()` hoặc `os.path.realpath` và kiểm tra tính phụ thuộc thư mục (containment check) trước khi mở file.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OWASP Top 10 - Path Traversal (https://owasp.org/www-community/attacks/Path_Traversal); CWE-22: Improper Limitation of a Pathname to a Restricted Directory.</t>
         </is>
       </c>
     </row>
